--- a/rcabinet-checker/docs/仕様書_rcabinet-checker_20260707.xlsx
+++ b/rcabinet-checker/docs/仕様書_rcabinet-checker_20260707.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ログの読み方" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="外部サービス一覧" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="動作確認のしかた" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="他PCへの反映手順" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -589,6 +590,229 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>やること</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>コマンド／操作</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>作業前の確認（重要）</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>コマンドプロンプトで toolsリポジトリのフォルダへ移動し、git status を実行</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>「nothing to commit, working tree clean」ならOK。もし未コミットの変更（赤い表示）がある場合は先に対処すること。過去に2つの作業場所で別々に開発して片方が消えかけた事故があるため、この確認は毎回行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>最新版を取得</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>git pull</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>反映作業は実質これだけ。今回の改修（タイトル照合・openBD/国会図書館対応）とテストスクリプト・本仕様書がまとめて取り込まれる</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>追加インストール</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>不要</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>今回の改修は新しいライブラリを使っていない（追加した機能はすべてPython標準機能＋導入済みライブラリで動く）。requirements.txt も変更なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>設定ファイル（secrets.toml）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>変更不要</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>openBD・国会図書館はAPIキー不要の無料サービスのため、新しい鍵や設定の追加はない。secrets.toml は従来のまま使える</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>動作確認（推奨・約1〜2分）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>python scripts/test_image_fetch.py</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>最後に表示される「最終サマリ」が3項目とも True なら正常。過去の誤画像事故2ケースの再発チェックが含まれている</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>アプリ起動</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>streamlit run streamlit_app.py</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>従来どおり。起動方法の詳細は HANDOVER_LOCAL_SETUP.md（リポジトリ内の引き継ぎ手順書）を参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>（任意）個別のJANで画像取得を試す</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>python scripts/fetch_preview.py &lt;JAN&gt; &lt;作品タイトル&gt; [set/tanpin/yoyaku] --out preview_out</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>本番と同じ流れで1件テストでき、加工済み画像が preview_out フォルダに保存される</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
